--- a/docs/dialogues-2026-10-15.xlsx
+++ b/docs/dialogues-2026-10-15.xlsx
@@ -3569,7 +3569,7 @@
       <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>renderForge()  · arena_app.js:32489</t>
+          <t>renderForge()  · arena_app.js:32566</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
       <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>In a fight, the first time a card needs Lumber  · arena_app.js:28464</t>
+          <t>In a fight, the first time a card needs Lumber  · arena_app.js:28467</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
       <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>In a fight, the first time a card needs Lumber  · arena_app.js:28464</t>
+          <t>In a fight, the first time a card needs Lumber  · arena_app.js:28467</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>In a fight, trying to send a 2nd card to the Graveyard in one turn  · arena_app.js:25905</t>
+          <t>In a fight, trying to send a 2nd card to the Graveyard in one turn  · arena_app.js:25908</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4321,7 @@
       <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>In a fight, trying to send a 2nd card to the Graveyard in one turn  · arena_app.js:25905</t>
+          <t>In a fight, trying to send a 2nd card to the Graveyard in one turn  · arena_app.js:25908</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Tutorial fights: remarks from your side  · arena_app.js:28489</t>
+          <t>Tutorial fights: remarks from your side  · arena_app.js:28492</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Tutorial fights: remarks from your side  · arena_app.js:28488</t>
+          <t>Tutorial fights: remarks from your side  · arena_app.js:28491</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Tutorial fights: remarks from your side  · arena_app.js:28484</t>
+          <t>Tutorial fights: remarks from your side  · arena_app.js:28487</t>
         </is>
       </c>
     </row>
